--- a/2026/GALERIA MITRE/Agosto/Agosto MITRE.xlsx
+++ b/2026/GALERIA MITRE/Agosto/Agosto MITRE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69A2216-2467-4912-8A09-1388AAD6F731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83D48E4-58AC-43BC-BFEE-D45D52F0D9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -23,16 +23,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$138</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="207">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -517,65 +512,12 @@
     <t>PREVISION ORDINARIA ARCA</t>
   </si>
   <si>
-    <t>Transfirio 104.955,29 el 07/07 y la pusimos impaga este mes debe abonar lo mismo</t>
-  </si>
-  <si>
     <t>Rocio Aylin</t>
   </si>
   <si>
-    <t>Juana acuña</t>
-  </si>
-  <si>
-    <t>Juana acuña menciona que: "La unidad funcional de Emilio Alonso Priero es la (UF55) No es la 45 como figura en la liquidación. Por favor podrían arreglarlo."</t>
-  </si>
-  <si>
-    <t>La de los depositos no identificados de rocio ailin es la of 57 - Este mes debe abonar $47.189,57 LO ABONA EL 11/08</t>
-  </si>
-  <si>
-    <t>UF 52 deposito $146.000 el 11/08 Mitre</t>
-  </si>
-  <si>
     <t>Luciano javier petrino</t>
   </si>
   <si>
-    <t xml:space="preserve">Local 11 y 12 </t>
-  </si>
-  <si>
-    <t>Luciano javier Petrino</t>
-  </si>
-  <si>
-    <t>Local 1</t>
-  </si>
-  <si>
-    <t>SICUSO</t>
-  </si>
-  <si>
-    <t>OF que abona con 46 centavos</t>
-  </si>
-  <si>
-    <t>Le pasamos mal un saldo anterior en junio, y eso genero una pelota de deuda indebida - Debe abonar $110.650,46</t>
-  </si>
-  <si>
-    <t>Deposito no identificado Junio $260.000 es del local 11 y 12 - Tambien Transfirio el 06/07 $300.000 - Chequear en el banco. Si todo esta correcto sus numeros a abonar son : L11: $430.854,11 y $235.930,12 - Abono el 12/08 $686.788,23</t>
-  </si>
-  <si>
-    <t>OF que abona con 41 centaos</t>
-  </si>
-  <si>
-    <t>Deposito $110.000 el 13/08</t>
-  </si>
-  <si>
-    <t>Laura BORAS deposito 14/08: LOC 17 $70.800
-OF 56 $110.600
-LOC 19 $156.900
-OF 12/22 $316.000
-LOC 9 $617.070
-LOC 8 $135.020</t>
-  </si>
-  <si>
-    <t>LAURA BORAS</t>
-  </si>
-  <si>
     <t>Debe abonar en Agosto 2026</t>
   </si>
   <si>
@@ -586,9 +528,6 @@
   </si>
   <si>
     <t>TOTAL:</t>
-  </si>
-  <si>
-    <t>Deposito no idetnficiado de Junio es de ella: por  $476368 - Debe abonar: $222,884,01</t>
   </si>
   <si>
     <t>Yesica Romina</t>
@@ -697,6 +636,27 @@
 Si bien el gasto a cubrir es de $2.500.000, el monto que se prorratea es superior, superando los $4.000.000. Esto se debe a que el gasto es exclusivo de las oficinas y, por lo tanto, los locales y sus respectivos porcentuales quedan excluidos del cálculo.
 Al no representar las oficinas el 100% de los porcentuales del edificio, si se prorratearan únicamente $2.500.000, la recaudación efectiva sería inferior al monto necesario.
 Por este motivo, se prorratea un importe superior a $4.000.000, de manera que, al distribuirlo exclusivamente entre las oficinas y aplicando sus respectivos porcentuales, se logre recaudar finalmente los $2.500.000 necesarios para afrontar el gasto del ascensor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uf que paga con 54 centavos abono $186.000 el 08/9
+</t>
+  </si>
+  <si>
+    <t>52??</t>
+  </si>
+  <si>
+    <t>Iparraguirre Inmobiliaria deposita $260.000 el 08/09 para la uf 52</t>
+  </si>
+  <si>
+    <t>local 19 deposito 21/9 $195.100
+local 8 deposito $154.100 el 16/09
+local 9 deposito $750.000 el 16/09
+oficina 56 deposito $191.570 el 16/09
+oficina 12 (101) deposito $550.000 el 16/09
+local 17 deposito $90.000 el 16/09</t>
+  </si>
+  <si>
+    <t>Laura boras</t>
   </si>
 </sst>
 </file>
@@ -887,7 +847,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -968,43 +928,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.499984740745262"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1368,7 +1304,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1562,228 +1498,211 @@
     <xf numFmtId="44" fontId="10" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="9" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="16" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="9" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1852,9 +1771,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1892,9 +1811,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1927,26 +1846,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1979,26 +1881,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2173,20 +2058,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L138"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="120" t="s">
         <v>64</v>
       </c>
@@ -2194,7 +2079,7 @@
       <c r="C1" s="122"/>
       <c r="D1" s="122"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="123" t="s">
         <v>125</v>
       </c>
@@ -2202,7 +2087,7 @@
       <c r="C2" s="123"/>
       <c r="D2" s="123"/>
     </row>
-    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="123" t="s">
         <v>70</v>
       </c>
@@ -2210,115 +2095,115 @@
       <c r="C3" s="123"/>
       <c r="D3" s="123"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="196" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="172" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="196"/>
+      <c r="B4" s="172"/>
       <c r="C4" s="124"/>
       <c r="D4" s="124"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="196"/>
-      <c r="B5" s="196"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="172"/>
+      <c r="B5" s="172"/>
       <c r="C5" s="124"/>
       <c r="D5" s="124"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="196"/>
-      <c r="B6" s="196"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="172"/>
+      <c r="B6" s="172"/>
       <c r="C6" s="124"/>
       <c r="D6" s="124"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="196"/>
-      <c r="B7" s="196"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="172"/>
+      <c r="B7" s="172"/>
       <c r="C7" s="124"/>
       <c r="D7" s="124"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="61"/>
       <c r="B8" s="61"/>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="61"/>
-      <c r="B9" s="195" t="s">
-        <v>185</v>
+      <c r="B9" s="181" t="s">
+        <v>168</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="61"/>
-      <c r="B10" s="195"/>
+      <c r="B10" s="181"/>
       <c r="C10" s="61"/>
       <c r="D10" s="61"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="61"/>
-      <c r="B11" s="195"/>
+      <c r="B11" s="181"/>
       <c r="C11" s="61"/>
       <c r="D11" s="61"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="61"/>
       <c r="B12" s="61"/>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="196" t="s">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="172" t="s">
         <v>147</v>
       </c>
-      <c r="B14" s="196"/>
-      <c r="C14" s="196"/>
-      <c r="D14" s="196"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="196"/>
-      <c r="B15" s="196"/>
-      <c r="C15" s="196"/>
-      <c r="D15" s="196"/>
-    </row>
-    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="196"/>
-      <c r="B16" s="196"/>
-      <c r="C16" s="196"/>
-      <c r="D16" s="196"/>
-    </row>
-    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="196"/>
-      <c r="B17" s="196"/>
-      <c r="C17" s="196"/>
-      <c r="D17" s="196"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="172"/>
+      <c r="C14" s="172"/>
+      <c r="D14" s="172"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="172"/>
+      <c r="B15" s="172"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="172"/>
+    </row>
+    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="172"/>
+      <c r="B16" s="172"/>
+      <c r="C16" s="172"/>
+      <c r="D16" s="172"/>
+    </row>
+    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="172"/>
+      <c r="B17" s="172"/>
+      <c r="C17" s="172"/>
+      <c r="D17" s="172"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="61"/>
       <c r="B18" s="61"/>
       <c r="C18" s="61"/>
       <c r="D18" s="61"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="125"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
       <c r="D19" s="61"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="61"/>
       <c r="B20" s="61"/>
       <c r="C20" s="61"/>
       <c r="D20" s="61"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="126" t="s">
         <v>26</v>
       </c>
@@ -2330,7 +2215,7 @@
       </c>
       <c r="F21" s="118"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>52</v>
       </c>
@@ -2340,36 +2225,36 @@
       <c r="E22" s="118"/>
       <c r="F22" s="118"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="193" t="s">
-        <v>186</v>
-      </c>
-      <c r="B23" s="194"/>
-      <c r="C23" s="241">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="B23" s="179"/>
+      <c r="C23" s="160">
         <v>1322255.05</v>
       </c>
       <c r="D23" s="46"/>
       <c r="E23" s="118"/>
       <c r="F23" s="118"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="46" t="s">
         <v>55</v>
       </c>
       <c r="B24" s="46"/>
-      <c r="C24" s="241">
+      <c r="C24" s="160">
         <v>-208255.05</v>
       </c>
       <c r="D24" s="46"/>
       <c r="E24" s="118"/>
       <c r="F24" s="118"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
         <v>54</v>
       </c>
       <c r="B25" s="46"/>
-      <c r="C25" s="241">
+      <c r="C25" s="160">
         <v>0</v>
       </c>
       <c r="D25" s="46"/>
@@ -2377,7 +2262,7 @@
       <c r="F25" s="118"/>
       <c r="G25" s="89"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="128" t="s">
         <v>53</v>
       </c>
@@ -2390,41 +2275,41 @@
       <c r="E26" s="118"/>
       <c r="F26" s="118"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="193" t="s">
-        <v>187</v>
-      </c>
-      <c r="B27" s="194"/>
-      <c r="C27" s="241">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="178" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="179"/>
+      <c r="C27" s="160">
         <v>941573.23</v>
       </c>
       <c r="D27" s="46"/>
       <c r="E27" s="118"/>
       <c r="F27" s="118"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="s">
         <v>55</v>
       </c>
       <c r="B28" s="46"/>
-      <c r="C28" s="241">
+      <c r="C28" s="160">
         <v>233039.23</v>
       </c>
       <c r="D28" s="71"/>
       <c r="E28" s="118"/>
       <c r="F28" s="118"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="46" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="46"/>
-      <c r="C29" s="241">
+      <c r="C29" s="160">
         <v>0</v>
       </c>
       <c r="D29" s="71"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="128" t="s">
         <v>53</v>
       </c>
@@ -2435,7 +2320,7 @@
       </c>
       <c r="D30" s="47"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
       <c r="C31" s="91">
@@ -2443,13 +2328,13 @@
       </c>
       <c r="D31" s="71"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
       <c r="C32" s="91"/>
       <c r="D32" s="71"/>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="128" t="s">
         <v>53</v>
       </c>
@@ -2460,7 +2345,7 @@
       </c>
       <c r="D33" s="47"/>
     </row>
-    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
         <v>0</v>
       </c>
@@ -2473,7 +2358,7 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -2482,59 +2367,59 @@
       <c r="D35" s="49"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="238" t="s">
-        <v>215</v>
-      </c>
-      <c r="B36" s="239"/>
-      <c r="C36" s="241">
+    <row r="36" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="176" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" s="177"/>
+      <c r="C36" s="160">
         <v>650000</v>
       </c>
       <c r="D36" s="78" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="238" t="s">
-        <v>201</v>
-      </c>
-      <c r="B37" s="239"/>
+    <row r="37" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="176" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" s="177"/>
       <c r="C37" s="81">
         <v>100000</v>
       </c>
       <c r="D37" s="75" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="238" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" s="239"/>
+    <row r="38" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="176" t="s">
+        <v>185</v>
+      </c>
+      <c r="B38" s="177"/>
       <c r="C38" s="81">
         <v>100000</v>
       </c>
       <c r="D38" s="75" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="238" t="s">
-        <v>204</v>
-      </c>
-      <c r="B39" s="239"/>
-      <c r="C39" s="241">
+    <row r="39" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="176" t="s">
+        <v>187</v>
+      </c>
+      <c r="B39" s="177"/>
+      <c r="C39" s="160">
         <v>200000</v>
       </c>
       <c r="D39" s="75" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="G39" s="4"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
         <v>34</v>
       </c>
@@ -2545,7 +2430,7 @@
         <v>1050000</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>49</v>
       </c>
@@ -2553,19 +2438,19 @@
       <c r="C41" s="13"/>
       <c r="D41" s="29"/>
     </row>
-    <row r="42" spans="1:7" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="238" t="s">
+    <row r="42" spans="1:7" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="176" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="239"/>
-      <c r="C42" s="242">
+      <c r="B42" s="177"/>
+      <c r="C42" s="161">
         <v>111108.81</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
         <v>1</v>
       </c>
@@ -2576,7 +2461,7 @@
         <v>111108.81</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>35</v>
       </c>
@@ -2584,7 +2469,7 @@
       <c r="C44" s="16"/>
       <c r="D44" s="51"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="71" t="s">
         <v>65</v>
       </c>
@@ -2595,24 +2480,24 @@
       <c r="D45" s="75"/>
       <c r="F45" s="72"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="238" t="s">
-        <v>197</v>
-      </c>
-      <c r="B46" s="239"/>
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="176" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="177"/>
       <c r="C46" s="81">
         <v>11596.99</v>
       </c>
       <c r="D46" s="77" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="F46" s="72"/>
     </row>
-    <row r="47" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="238" t="s">
-        <v>195</v>
-      </c>
-      <c r="B47" s="239"/>
+    <row r="47" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="176" t="s">
+        <v>178</v>
+      </c>
+      <c r="B47" s="177"/>
       <c r="C47" s="81">
         <v>11930.96</v>
       </c>
@@ -2622,7 +2507,7 @@
       </c>
       <c r="F47" s="72"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="71" t="s">
         <v>66</v>
       </c>
@@ -2631,10 +2516,10 @@
         <v>101872.21</v>
       </c>
       <c r="D48" s="77" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="71" t="s">
         <v>67</v>
       </c>
@@ -2647,7 +2532,7 @@
         <v>Debito 12/08</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="71" t="s">
         <v>68</v>
       </c>
@@ -2660,7 +2545,7 @@
         <v>Debito 12/08</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
         <v>2</v>
       </c>
@@ -2671,7 +2556,7 @@
         <v>357956.04000000004</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>37</v>
       </c>
@@ -2679,7 +2564,7 @@
       <c r="C52" s="16"/>
       <c r="D52" s="51"/>
     </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="71" t="s">
         <v>127</v>
       </c>
@@ -2688,10 +2573,10 @@
         <v>335271.92</v>
       </c>
       <c r="D53" s="77" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="71" t="s">
         <v>126</v>
       </c>
@@ -2704,31 +2589,31 @@
         <v>Debito 12/08</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="71" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="B55" s="71"/>
       <c r="C55" s="81">
         <v>1432816.72</v>
       </c>
       <c r="D55" s="75" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="71" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="B56" s="71"/>
       <c r="C56" s="81">
         <v>1411636.23</v>
       </c>
       <c r="D56" s="77" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="71" t="s">
         <v>128</v>
       </c>
@@ -2737,22 +2622,22 @@
         <v>36065.47</v>
       </c>
       <c r="D57" s="77" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="B58" s="240"/>
+      <c r="B58" s="159"/>
       <c r="C58" s="81">
         <v>83831</v>
       </c>
       <c r="D58" s="75" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="11" t="s">
         <v>3</v>
       </c>
@@ -2763,7 +2648,7 @@
         <v>3299621.3400000003</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>36</v>
       </c>
@@ -2771,74 +2656,74 @@
       <c r="C60" s="15"/>
       <c r="D60" s="53"/>
     </row>
-    <row r="61" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="238" t="s">
-        <v>198</v>
-      </c>
-      <c r="B61" s="239"/>
+    <row r="61" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="176" t="s">
+        <v>181</v>
+      </c>
+      <c r="B61" s="177"/>
       <c r="C61" s="81">
         <v>202000</v>
       </c>
       <c r="D61" s="75" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="238" t="s">
-        <v>199</v>
-      </c>
-      <c r="B62" s="239"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="176" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" s="177"/>
       <c r="C62" s="81">
         <v>202000</v>
       </c>
       <c r="D62" s="75" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="G62" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="198" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="238" t="s">
-        <v>206</v>
-      </c>
-      <c r="B63" s="239"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="198" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="176" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" s="177"/>
       <c r="C63" s="81">
         <v>650000</v>
       </c>
       <c r="D63" s="75" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="F63" s="22"/>
     </row>
-    <row r="64" spans="1:7" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="238" t="s">
-        <v>207</v>
-      </c>
-      <c r="B64" s="239"/>
+    <row r="64" spans="1:7" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="176" t="s">
+        <v>190</v>
+      </c>
+      <c r="B64" s="177"/>
       <c r="C64" s="81">
         <v>166345.46</v>
       </c>
       <c r="D64" s="75" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="F64" s="22"/>
     </row>
-    <row r="65" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="238" t="s">
-        <v>209</v>
-      </c>
-      <c r="B65" s="239"/>
+    <row r="65" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="176" t="s">
+        <v>192</v>
+      </c>
+      <c r="B65" s="177"/>
       <c r="C65" s="81">
         <v>185794.9</v>
       </c>
       <c r="D65" s="75" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="E65" s="116"/>
       <c r="F65" s="22"/>
     </row>
-    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="11" t="s">
         <v>11</v>
       </c>
@@ -2849,7 +2734,7 @@
         <v>1406140.3599999999</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
         <v>29</v>
       </c>
@@ -2857,17 +2742,17 @@
       <c r="C67" s="7"/>
       <c r="D67" s="53"/>
     </row>
-    <row r="68" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="193" t="s">
+    <row r="68" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="178" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="194"/>
+      <c r="B68" s="179"/>
       <c r="C68" s="81">
         <v>75000</v>
       </c>
       <c r="D68" s="57"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="46" t="s">
         <v>71</v>
       </c>
@@ -2877,7 +2762,7 @@
       </c>
       <c r="D69" s="55"/>
     </row>
-    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="130" t="s">
         <v>34</v>
       </c>
@@ -2888,30 +2773,30 @@
         <v>247775.23</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="46"/>
       <c r="B71" s="46"/>
       <c r="C71" s="46"/>
       <c r="D71" s="59"/>
     </row>
-    <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="197" t="s">
+    <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="173" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="198"/>
-      <c r="C72" s="199"/>
+      <c r="B72" s="174"/>
+      <c r="C72" s="175"/>
       <c r="D72" s="60">
         <v>1000000</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="131"/>
       <c r="B73" s="61"/>
       <c r="C73" s="61"/>
       <c r="D73" s="62"/>
       <c r="E73" s="22"/>
     </row>
-    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="132" t="s">
         <v>30</v>
       </c>
@@ -2924,20 +2809,20 @@
       <c r="E74" s="22"/>
       <c r="F74" s="22"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="61"/>
       <c r="B75" s="61"/>
       <c r="C75" s="61"/>
       <c r="D75" s="61"/>
       <c r="F75" s="73"/>
     </row>
-    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="61"/>
       <c r="B76" s="61"/>
       <c r="C76" s="61"/>
       <c r="D76" s="61"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="126" t="s">
         <v>39</v>
       </c>
@@ -2945,25 +2830,25 @@
       <c r="C77" s="65"/>
       <c r="D77" s="66"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="193"/>
-      <c r="B78" s="194"/>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="178"/>
+      <c r="B78" s="179"/>
       <c r="C78" s="54"/>
       <c r="D78" s="52"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="193"/>
-      <c r="B79" s="194"/>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="178"/>
+      <c r="B79" s="179"/>
       <c r="C79" s="54"/>
       <c r="D79" s="52"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="117"/>
       <c r="B80" s="134"/>
       <c r="C80" s="54"/>
       <c r="D80" s="52"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="135"/>
       <c r="B81" s="136"/>
       <c r="C81" s="137"/>
@@ -2972,19 +2857,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="61"/>
       <c r="B82" s="61"/>
       <c r="C82" s="61"/>
       <c r="D82" s="61"/>
     </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="61"/>
       <c r="B83" s="61"/>
       <c r="C83" s="61"/>
       <c r="D83" s="61"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="138" t="s">
         <v>40</v>
       </c>
@@ -2994,13 +2879,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="61"/>
       <c r="B85" s="61"/>
       <c r="C85" s="61"/>
       <c r="D85" s="61"/>
     </row>
-    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="132" t="s">
         <v>41</v>
       </c>
@@ -3011,13 +2896,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="61"/>
       <c r="B87" s="61"/>
       <c r="C87" s="61"/>
       <c r="D87" s="61"/>
     </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="141" t="s">
         <v>31</v>
       </c>
@@ -3028,7 +2913,7 @@
       <c r="C88" s="143"/>
       <c r="D88" s="61"/>
     </row>
-    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="141" t="s">
         <v>32</v>
       </c>
@@ -3039,7 +2924,7 @@
       <c r="C89" s="61"/>
       <c r="D89" s="61"/>
     </row>
-    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="141" t="s">
         <v>42</v>
       </c>
@@ -3050,7 +2935,7 @@
       <c r="C90" s="61"/>
       <c r="D90" s="61"/>
     </row>
-    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="141" t="s">
         <v>59</v>
       </c>
@@ -3061,141 +2946,141 @@
       <c r="C91" s="61"/>
       <c r="D91" s="61"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="245" t="s">
-        <v>218</v>
-      </c>
-      <c r="B94" s="246"/>
-      <c r="C94" s="246"/>
-      <c r="D94" s="246"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="246"/>
-      <c r="B95" s="246"/>
-      <c r="C95" s="246"/>
-      <c r="D95" s="246"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="246"/>
-      <c r="B96" s="246"/>
-      <c r="C96" s="246"/>
-      <c r="D96" s="246"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="246"/>
-      <c r="B97" s="246"/>
-      <c r="C97" s="246"/>
-      <c r="D97" s="246"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="246"/>
-      <c r="B98" s="246"/>
-      <c r="C98" s="246"/>
-      <c r="D98" s="246"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="246"/>
-      <c r="B99" s="246"/>
-      <c r="C99" s="246"/>
-      <c r="D99" s="246"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="246"/>
-      <c r="B100" s="246"/>
-      <c r="C100" s="246"/>
-      <c r="D100" s="246"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="246"/>
-      <c r="B101" s="246"/>
-      <c r="C101" s="246"/>
-      <c r="D101" s="246"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="246"/>
-      <c r="B102" s="246"/>
-      <c r="C102" s="246"/>
-      <c r="D102" s="246"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="246"/>
-      <c r="B103" s="246"/>
-      <c r="C103" s="246"/>
-      <c r="D103" s="246"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="246"/>
-      <c r="B104" s="246"/>
-      <c r="C104" s="246"/>
-      <c r="D104" s="246"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="246"/>
-      <c r="B105" s="246"/>
-      <c r="C105" s="246"/>
-      <c r="D105" s="246"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="246"/>
-      <c r="B106" s="246"/>
-      <c r="C106" s="246"/>
-      <c r="D106" s="246"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="246"/>
-      <c r="B107" s="246"/>
-      <c r="C107" s="246"/>
-      <c r="D107" s="246"/>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="246"/>
-      <c r="B108" s="246"/>
-      <c r="C108" s="246"/>
-      <c r="D108" s="246"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="246"/>
-      <c r="B109" s="246"/>
-      <c r="C109" s="246"/>
-      <c r="D109" s="246"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="246"/>
-      <c r="B110" s="246"/>
-      <c r="C110" s="246"/>
-      <c r="D110" s="246"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="246"/>
-      <c r="B111" s="246"/>
-      <c r="C111" s="246"/>
-      <c r="D111" s="246"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="246"/>
-      <c r="B112" s="246"/>
-      <c r="C112" s="246"/>
-      <c r="D112" s="246"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="246"/>
-      <c r="B113" s="246"/>
-      <c r="C113" s="246"/>
-      <c r="D113" s="246"/>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="246"/>
-      <c r="B114" s="246"/>
-      <c r="C114" s="246"/>
-      <c r="D114" s="246"/>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="182" t="s">
+        <v>201</v>
+      </c>
+      <c r="B94" s="183"/>
+      <c r="C94" s="183"/>
+      <c r="D94" s="183"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="183"/>
+      <c r="B95" s="183"/>
+      <c r="C95" s="183"/>
+      <c r="D95" s="183"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="183"/>
+      <c r="B96" s="183"/>
+      <c r="C96" s="183"/>
+      <c r="D96" s="183"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="183"/>
+      <c r="B97" s="183"/>
+      <c r="C97" s="183"/>
+      <c r="D97" s="183"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="183"/>
+      <c r="B98" s="183"/>
+      <c r="C98" s="183"/>
+      <c r="D98" s="183"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="183"/>
+      <c r="B99" s="183"/>
+      <c r="C99" s="183"/>
+      <c r="D99" s="183"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="183"/>
+      <c r="B100" s="183"/>
+      <c r="C100" s="183"/>
+      <c r="D100" s="183"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="183"/>
+      <c r="B101" s="183"/>
+      <c r="C101" s="183"/>
+      <c r="D101" s="183"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="183"/>
+      <c r="B102" s="183"/>
+      <c r="C102" s="183"/>
+      <c r="D102" s="183"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="183"/>
+      <c r="B103" s="183"/>
+      <c r="C103" s="183"/>
+      <c r="D103" s="183"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="183"/>
+      <c r="B104" s="183"/>
+      <c r="C104" s="183"/>
+      <c r="D104" s="183"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="183"/>
+      <c r="B105" s="183"/>
+      <c r="C105" s="183"/>
+      <c r="D105" s="183"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="183"/>
+      <c r="B106" s="183"/>
+      <c r="C106" s="183"/>
+      <c r="D106" s="183"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="183"/>
+      <c r="B107" s="183"/>
+      <c r="C107" s="183"/>
+      <c r="D107" s="183"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="183"/>
+      <c r="B108" s="183"/>
+      <c r="C108" s="183"/>
+      <c r="D108" s="183"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="183"/>
+      <c r="B109" s="183"/>
+      <c r="C109" s="183"/>
+      <c r="D109" s="183"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="183"/>
+      <c r="B110" s="183"/>
+      <c r="C110" s="183"/>
+      <c r="D110" s="183"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="183"/>
+      <c r="B111" s="183"/>
+      <c r="C111" s="183"/>
+      <c r="D111" s="183"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="183"/>
+      <c r="B112" s="183"/>
+      <c r="C112" s="183"/>
+      <c r="D112" s="183"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="183"/>
+      <c r="B113" s="183"/>
+      <c r="C113" s="183"/>
+      <c r="D113" s="183"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="183"/>
+      <c r="B114" s="183"/>
+      <c r="C114" s="183"/>
+      <c r="D114" s="183"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B117" s="19"/>
     </row>
-    <row r="118" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9" t="s">
         <v>33</v>
       </c>
@@ -3203,7 +3088,7 @@
         <v>2649072.209999999</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="94" t="s">
         <v>62</v>
       </c>
@@ -3212,7 +3097,7 @@
         <v>10043048.190000001</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="94" t="s">
         <v>61</v>
       </c>
@@ -3221,39 +3106,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B121" s="74">
         <v>-92118</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="B122" s="74">
         <v>-262000</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="B123" s="74">
         <v>-104955.29</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B124" s="74">
         <v>-260000</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>72</v>
       </c>
@@ -3262,7 +3147,7 @@
         <v>-10002</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>43</v>
       </c>
@@ -3271,7 +3156,7 @@
         <v>-8761214.2400000002</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>44</v>
       </c>
@@ -3280,7 +3165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>11</v>
       </c>
@@ -3291,52 +3176,52 @@
       <c r="C128" s="22"/>
       <c r="D128" s="92"/>
     </row>
-    <row r="129" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1"/>
       <c r="B129" s="95"/>
       <c r="D129" s="92"/>
     </row>
-    <row r="130" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="106" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="B130" s="107">
         <v>1397979.91</v>
       </c>
       <c r="D130" s="92"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" s="243" t="s">
-        <v>216</v>
-      </c>
-      <c r="B131" s="244">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A131" s="162" t="s">
+        <v>199</v>
+      </c>
+      <c r="B131" s="163">
         <f>1465817.44-B130</f>
         <v>67837.530000000028</v>
       </c>
       <c r="D131" s="92"/>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D132" s="93"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A133" s="192" t="s">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A133" s="180" t="s">
         <v>50</v>
       </c>
-      <c r="B133" s="192"/>
-    </row>
-    <row r="134" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="192"/>
-      <c r="B134" s="192"/>
-    </row>
-    <row r="135" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B133" s="180"/>
+    </row>
+    <row r="134" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="180"/>
+      <c r="B134" s="180"/>
+    </row>
+    <row r="135" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="67"/>
       <c r="B135" s="14"/>
     </row>
-    <row r="136" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="67"/>
       <c r="B136" s="14"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="23" t="s">
         <v>11</v>
       </c>
@@ -3345,11 +3230,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L138" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A133:B134"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A94:D114"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A72:C72"/>
@@ -3362,17 +3258,6 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A133:B134"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A94:D114"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3383,41 +3268,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.44140625" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" customWidth="1"/>
-    <col min="12" max="13" width="12.42578125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" customWidth="1"/>
+    <col min="12" max="13" width="12.44140625" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="184" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="208"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="186"/>
       <c r="K1" s="102" t="s">
         <v>4</v>
       </c>
@@ -3433,17 +3318,17 @@
         <v>8136047.4719999991</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="209"/>
-      <c r="C2" s="210"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="210"/>
-      <c r="J2" s="211"/>
+      <c r="B2" s="187"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="189"/>
       <c r="K2" s="104" t="s">
         <v>63</v>
       </c>
@@ -3455,155 +3340,155 @@
       </c>
       <c r="P2" s="101"/>
     </row>
-    <row r="3" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="178"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="179"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="179"/>
-      <c r="K3" s="188" t="s">
-        <v>214</v>
-      </c>
-      <c r="L3" s="189"/>
-      <c r="M3" s="189"/>
-      <c r="N3" s="189"/>
-      <c r="O3" s="190">
+      <c r="B3" s="146"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="155" t="s">
+        <v>197</v>
+      </c>
+      <c r="L3" s="156"/>
+      <c r="M3" s="156"/>
+      <c r="N3" s="156"/>
+      <c r="O3" s="157">
         <f>700+4389375+300+150+50+10+1+1</f>
         <v>4390587</v>
       </c>
-      <c r="P3" s="191"/>
-    </row>
-    <row r="4" spans="1:19" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P3" s="158"/>
+    </row>
+    <row r="4" spans="1:19" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="223" t="s">
+      <c r="B4" s="203" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="224"/>
-      <c r="D4" s="224"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="224"/>
-      <c r="G4" s="224"/>
-      <c r="H4" s="224"/>
-      <c r="I4" s="224"/>
-      <c r="J4" s="224"/>
-      <c r="K4" s="224"/>
-      <c r="L4" s="224"/>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="224"/>
-      <c r="P4" s="225"/>
-    </row>
-    <row r="5" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="204"/>
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="204"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="204"/>
+      <c r="I4" s="204"/>
+      <c r="J4" s="204"/>
+      <c r="K4" s="204"/>
+      <c r="L4" s="204"/>
+      <c r="M4" s="204"/>
+      <c r="N4" s="204"/>
+      <c r="O4" s="204"/>
+      <c r="P4" s="205"/>
+    </row>
+    <row r="5" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
-      <c r="B5" s="226" t="s">
+      <c r="B5" s="206" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="227"/>
-      <c r="D5" s="227"/>
-      <c r="E5" s="227"/>
-      <c r="F5" s="227"/>
-      <c r="G5" s="227"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="227"/>
-      <c r="K5" s="227"/>
-      <c r="L5" s="227"/>
-      <c r="M5" s="227"/>
-      <c r="N5" s="227"/>
-      <c r="O5" s="227"/>
-      <c r="P5" s="228"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="200" t="s">
+      <c r="C5" s="207"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="207"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="207"/>
+      <c r="L5" s="207"/>
+      <c r="M5" s="207"/>
+      <c r="N5" s="207"/>
+      <c r="O5" s="207"/>
+      <c r="P5" s="208"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="202" t="s">
+      <c r="B6" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="204" t="s">
+      <c r="C6" s="193" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="204" t="s">
+      <c r="D6" s="193" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="204" t="s">
+      <c r="E6" s="193" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="204" t="s">
+      <c r="F6" s="193" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="204" t="s">
+      <c r="G6" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="204" t="s">
+      <c r="H6" s="193" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="218" t="s">
+      <c r="I6" s="198" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="216" t="s">
+      <c r="J6" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="216" t="s">
+      <c r="K6" s="195" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="216" t="s">
+      <c r="L6" s="195" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="216" t="s">
-        <v>217</v>
-      </c>
-      <c r="N6" s="221" t="s">
+      <c r="M6" s="195" t="s">
+        <v>200</v>
+      </c>
+      <c r="N6" s="201" t="s">
         <v>58</v>
       </c>
       <c r="O6" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="212" t="s">
+      <c r="P6" s="190" t="s">
         <v>56</v>
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="201"/>
-      <c r="B7" s="203"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="215"/>
-      <c r="I7" s="219"/>
-      <c r="J7" s="217"/>
-      <c r="K7" s="220"/>
-      <c r="L7" s="217"/>
-      <c r="M7" s="217"/>
-      <c r="N7" s="222"/>
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="210"/>
+      <c r="B7" s="212"/>
+      <c r="C7" s="197"/>
+      <c r="D7" s="197"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="197"/>
+      <c r="G7" s="197"/>
+      <c r="H7" s="194"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="196"/>
+      <c r="K7" s="200"/>
+      <c r="L7" s="196"/>
+      <c r="M7" s="196"/>
+      <c r="N7" s="202"/>
       <c r="O7" s="26" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="P7" s="213"/>
-    </row>
-    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P7" s="191"/>
+    </row>
+    <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="181">
-        <v>0</v>
-      </c>
-      <c r="C8" s="181" t="s">
+      <c r="B8" s="149">
+        <v>0</v>
+      </c>
+      <c r="C8" s="149" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="181" t="s">
+      <c r="D8" s="149" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="182">
+      <c r="E8" s="150">
         <v>1.58</v>
       </c>
       <c r="F8" s="32">
@@ -3629,7 +3514,7 @@
         <f t="shared" ref="L8:L39" si="1">O$1*E8%</f>
         <v>154227.18499200002</v>
       </c>
-      <c r="M8" s="186"/>
+      <c r="M8" s="153"/>
       <c r="N8" s="36">
         <v>0</v>
       </c>
@@ -3645,18 +3530,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="180"/>
-      <c r="B9" s="181">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="148"/>
+      <c r="B9" s="149">
         <v>1</v>
       </c>
-      <c r="C9" s="181" t="s">
+      <c r="C9" s="149" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="181" t="s">
+      <c r="D9" s="149" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="182">
+      <c r="E9" s="150">
         <v>2.91</v>
       </c>
       <c r="F9" s="32">
@@ -3683,7 +3568,7 @@
         <f t="shared" si="1"/>
         <v>284051.33438399999</v>
       </c>
-      <c r="M9" s="186"/>
+      <c r="M9" s="153"/>
       <c r="N9" s="36">
         <v>0</v>
       </c>
@@ -3700,24 +3585,24 @@
         <v>0.01</v>
       </c>
       <c r="R9" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="181">
+      <c r="B10" s="149">
         <f>B9+1</f>
         <v>2</v>
       </c>
-      <c r="C10" s="181" t="s">
+      <c r="C10" s="149" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="181" t="s">
+      <c r="D10" s="149" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="182">
+      <c r="E10" s="150">
         <v>1.94</v>
       </c>
       <c r="F10" s="32">
@@ -3743,7 +3628,7 @@
         <f t="shared" si="1"/>
         <v>189367.55625600001</v>
       </c>
-      <c r="M10" s="187"/>
+      <c r="M10" s="154"/>
       <c r="N10" s="86">
         <v>0</v>
       </c>
@@ -3760,24 +3645,24 @@
         <v>0.02</v>
       </c>
       <c r="R10" s="22" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="181">
+      <c r="B11" s="149">
         <f t="shared" ref="B11:B46" si="6">B10+1</f>
         <v>3</v>
       </c>
-      <c r="C11" s="181" t="s">
+      <c r="C11" s="149" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="183" t="s">
+      <c r="D11" s="151" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="182">
+      <c r="E11" s="150">
         <v>1.78</v>
       </c>
       <c r="F11" s="32">
@@ -3804,7 +3689,7 @@
         <f t="shared" si="1"/>
         <v>173749.613472</v>
       </c>
-      <c r="M11" s="187"/>
+      <c r="M11" s="154"/>
       <c r="N11" s="86">
         <v>0</v>
       </c>
@@ -3821,21 +3706,21 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="181">
+      <c r="B12" s="149">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="C12" s="181" t="s">
+      <c r="C12" s="149" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="181" t="s">
+      <c r="D12" s="149" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="182">
+      <c r="E12" s="150">
         <v>1.62</v>
       </c>
       <c r="F12" s="32">
@@ -3862,7 +3747,7 @@
         <f t="shared" si="1"/>
         <v>158131.67068800004</v>
       </c>
-      <c r="M12" s="186"/>
+      <c r="M12" s="153"/>
       <c r="N12" s="36">
         <v>0</v>
       </c>
@@ -3883,21 +3768,21 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="181">
+      <c r="B13" s="149">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="C13" s="181" t="s">
+      <c r="C13" s="149" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="181" t="s">
+      <c r="D13" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="182">
+      <c r="E13" s="150">
         <v>1.94</v>
       </c>
       <c r="F13" s="32">
@@ -3923,7 +3808,7 @@
         <f t="shared" si="1"/>
         <v>189367.55625600001</v>
       </c>
-      <c r="M13" s="186"/>
+      <c r="M13" s="153"/>
       <c r="N13" s="36">
         <v>0</v>
       </c>
@@ -3941,19 +3826,19 @@
       </c>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="119"/>
-      <c r="B14" s="181">
+      <c r="B14" s="149">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="C14" s="181" t="s">
+      <c r="C14" s="149" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="181" t="s">
+      <c r="D14" s="149" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="182">
+      <c r="E14" s="150">
         <v>1.78</v>
       </c>
       <c r="F14" s="32">
@@ -3979,7 +3864,7 @@
         <f t="shared" si="1"/>
         <v>173749.613472</v>
       </c>
-      <c r="M14" s="186"/>
+      <c r="M14" s="153"/>
       <c r="N14" s="36">
         <v>0</v>
       </c>
@@ -3997,19 +3882,19 @@
       </c>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="119"/>
-      <c r="B15" s="181">
+      <c r="B15" s="149">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="C15" s="181" t="s">
+      <c r="C15" s="149" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="181" t="s">
+      <c r="D15" s="149" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="182">
+      <c r="E15" s="150">
         <v>1.62</v>
       </c>
       <c r="F15" s="32">
@@ -4036,7 +3921,7 @@
         <f t="shared" si="1"/>
         <v>158131.67068800004</v>
       </c>
-      <c r="M15" s="186"/>
+      <c r="M15" s="153"/>
       <c r="N15" s="36">
         <v>0</v>
       </c>
@@ -4057,19 +3942,19 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="119"/>
-      <c r="B16" s="181">
+      <c r="B16" s="149">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="C16" s="181" t="s">
+      <c r="C16" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="181" t="s">
+      <c r="D16" s="149" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="182">
+      <c r="E16" s="150">
         <v>1.62</v>
       </c>
       <c r="F16" s="32">
@@ -4095,7 +3980,7 @@
         <f t="shared" si="1"/>
         <v>158131.67068800004</v>
       </c>
-      <c r="M16" s="187"/>
+      <c r="M16" s="154"/>
       <c r="N16" s="86">
         <v>0</v>
       </c>
@@ -4113,19 +3998,19 @@
       </c>
       <c r="S16" s="22"/>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="119"/>
-      <c r="B17" s="181">
+      <c r="B17" s="149">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="C17" s="181" t="s">
+      <c r="C17" s="149" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="181" t="s">
+      <c r="D17" s="149" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="182">
+      <c r="E17" s="150">
         <v>7.59</v>
       </c>
       <c r="F17" s="32">
@@ -4151,7 +4036,7 @@
         <f t="shared" si="1"/>
         <v>740876.16081599996</v>
       </c>
-      <c r="M17" s="187"/>
+      <c r="M17" s="154"/>
       <c r="N17" s="86">
         <v>0</v>
       </c>
@@ -4169,19 +4054,19 @@
       </c>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="119"/>
-      <c r="B18" s="181">
+      <c r="B18" s="149">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C18" s="181" t="s">
+      <c r="C18" s="149" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="181" t="s">
+      <c r="D18" s="149" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="182">
+      <c r="E18" s="150">
         <v>1.62</v>
       </c>
       <c r="F18" s="32">
@@ -4208,7 +4093,7 @@
         <f t="shared" si="1"/>
         <v>158131.67068800004</v>
       </c>
-      <c r="M18" s="187"/>
+      <c r="M18" s="154"/>
       <c r="N18" s="86">
         <v>0</v>
       </c>
@@ -4229,19 +4114,19 @@
       </c>
       <c r="S18" s="22"/>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="119"/>
-      <c r="B19" s="181">
+      <c r="B19" s="149">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="C19" s="181" t="s">
+      <c r="C19" s="149" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="181" t="s">
+      <c r="D19" s="149" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="182">
+      <c r="E19" s="150">
         <v>1.78</v>
       </c>
       <c r="F19" s="32">
@@ -4268,7 +4153,7 @@
         <f t="shared" si="1"/>
         <v>173749.613472</v>
       </c>
-      <c r="M19" s="187"/>
+      <c r="M19" s="154"/>
       <c r="N19" s="86">
         <v>0</v>
       </c>
@@ -4285,23 +4170,23 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="R19" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="S19" s="22"/>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="119"/>
-      <c r="B20" s="181">
+      <c r="B20" s="149">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="C20" s="181" t="s">
+      <c r="C20" s="149" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="181" t="s">
+      <c r="D20" s="149" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="182">
+      <c r="E20" s="150">
         <v>1.3</v>
       </c>
       <c r="F20" s="32">
@@ -4328,7 +4213,7 @@
         <f t="shared" si="1"/>
         <v>126895.78512000002</v>
       </c>
-      <c r="M20" s="187"/>
+      <c r="M20" s="154"/>
       <c r="N20" s="86">
         <v>0</v>
       </c>
@@ -4345,23 +4230,23 @@
         <v>0.11999999999999998</v>
       </c>
       <c r="R20" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="119"/>
-      <c r="B21" s="181">
+      <c r="B21" s="149">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="C21" s="181" t="s">
+      <c r="C21" s="149" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="181" t="s">
+      <c r="D21" s="149" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="182">
+      <c r="E21" s="150">
         <v>1.38</v>
       </c>
       <c r="F21" s="32">
@@ -4388,7 +4273,7 @@
         <f t="shared" si="1"/>
         <v>134704.75651199999</v>
       </c>
-      <c r="M21" s="187"/>
+      <c r="M21" s="154"/>
       <c r="N21" s="86">
         <v>0</v>
       </c>
@@ -4409,19 +4294,19 @@
       </c>
       <c r="S21" s="22"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="119"/>
-      <c r="B22" s="181">
+      <c r="B22" s="149">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="C22" s="181" t="s">
+      <c r="C22" s="149" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="181" t="s">
+      <c r="D22" s="149" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="182">
+      <c r="E22" s="150">
         <v>1.87</v>
       </c>
       <c r="F22" s="32">
@@ -4448,7 +4333,7 @@
         <f t="shared" si="1"/>
         <v>182534.70628800002</v>
       </c>
-      <c r="M22" s="187"/>
+      <c r="M22" s="154"/>
       <c r="N22" s="86">
         <v>0</v>
       </c>
@@ -4469,19 +4354,19 @@
       </c>
       <c r="S22" s="22"/>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="119"/>
-      <c r="B23" s="181">
+      <c r="B23" s="149">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C23" s="181" t="s">
+      <c r="C23" s="149" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="181" t="s">
+      <c r="D23" s="149" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="182">
+      <c r="E23" s="150">
         <v>2.91</v>
       </c>
       <c r="F23" s="32">
@@ -4507,7 +4392,7 @@
         <f t="shared" si="1"/>
         <v>284051.33438399999</v>
       </c>
-      <c r="M23" s="187"/>
+      <c r="M23" s="154"/>
       <c r="N23" s="86">
         <v>0</v>
       </c>
@@ -4524,23 +4409,23 @@
         <v>0.15</v>
       </c>
       <c r="R23" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="S23" s="22"/>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="119"/>
-      <c r="B24" s="181">
+      <c r="B24" s="149">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C24" s="181" t="s">
+      <c r="C24" s="149" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="181" t="s">
+      <c r="D24" s="149" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="182">
+      <c r="E24" s="150">
         <v>2.14</v>
       </c>
       <c r="F24" s="32">
@@ -4566,7 +4451,7 @@
         <f t="shared" si="1"/>
         <v>208889.98473600004</v>
       </c>
-      <c r="M24" s="187"/>
+      <c r="M24" s="154"/>
       <c r="N24" s="86">
         <v>0</v>
       </c>
@@ -4587,21 +4472,21 @@
       </c>
       <c r="S24" s="22"/>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="181">
+      <c r="B25" s="149">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="C25" s="181" t="s">
+      <c r="C25" s="149" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="181" t="s">
+      <c r="D25" s="149" t="s">
         <v>82</v>
       </c>
-      <c r="E25" s="182">
+      <c r="E25" s="150">
         <v>0.89</v>
       </c>
       <c r="F25" s="32">
@@ -4627,7 +4512,7 @@
         <f t="shared" si="1"/>
         <v>86874.806735999999</v>
       </c>
-      <c r="M25" s="187"/>
+      <c r="M25" s="154"/>
       <c r="N25" s="86">
         <v>0</v>
       </c>
@@ -4644,21 +4529,21 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="181">
+      <c r="B26" s="149">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="C26" s="181" t="s">
+      <c r="C26" s="149" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="181" t="s">
+      <c r="D26" s="149" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="182">
+      <c r="E26" s="150">
         <v>0.95</v>
       </c>
       <c r="F26" s="32">
@@ -4684,7 +4569,7 @@
         <f t="shared" si="1"/>
         <v>92731.535279999996</v>
       </c>
-      <c r="M26" s="187"/>
+      <c r="M26" s="154"/>
       <c r="N26" s="86">
         <v>0</v>
       </c>
@@ -4703,21 +4588,21 @@
       <c r="R26" s="73"/>
       <c r="S26" s="72"/>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="181">
+      <c r="B27" s="149">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="C27" s="181" t="s">
+      <c r="C27" s="149" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="181" t="s">
+      <c r="D27" s="149" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="182">
+      <c r="E27" s="150">
         <v>1.94</v>
       </c>
       <c r="F27" s="32">
@@ -4743,7 +4628,7 @@
         <f t="shared" si="1"/>
         <v>189367.55625600001</v>
       </c>
-      <c r="M27" s="187"/>
+      <c r="M27" s="154"/>
       <c r="N27" s="86">
         <v>0</v>
       </c>
@@ -4760,21 +4645,21 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="181">
+      <c r="B28" s="149">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="C28" s="181" t="s">
+      <c r="C28" s="149" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="181" t="s">
+      <c r="D28" s="149" t="s">
         <v>89</v>
       </c>
-      <c r="E28" s="182">
+      <c r="E28" s="150">
         <v>1.84</v>
       </c>
       <c r="F28" s="32">
@@ -4800,7 +4685,7 @@
         <f t="shared" si="1"/>
         <v>179606.34201600001</v>
       </c>
-      <c r="M28" s="187"/>
+      <c r="M28" s="154"/>
       <c r="N28" s="86">
         <v>0</v>
       </c>
@@ -4817,21 +4702,21 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="181">
+      <c r="B29" s="149">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="C29" s="181">
+      <c r="C29" s="149">
         <v>1106</v>
       </c>
-      <c r="D29" s="181" t="s">
+      <c r="D29" s="149" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="182">
+      <c r="E29" s="150">
         <v>5.12</v>
       </c>
       <c r="F29" s="32">
@@ -4877,21 +4762,21 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="181">
+      <c r="B30" s="227">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="C30" s="181">
+      <c r="C30" s="227">
         <v>1101</v>
       </c>
-      <c r="D30" s="181" t="s">
+      <c r="D30" s="227" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="182">
+      <c r="E30" s="150">
         <v>3.88</v>
       </c>
       <c r="F30" s="32">
@@ -4941,21 +4826,21 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="181">
+      <c r="B31" s="149">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="C31" s="181">
+      <c r="C31" s="149">
         <v>1102</v>
       </c>
-      <c r="D31" s="181" t="s">
+      <c r="D31" s="149" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="182">
+      <c r="E31" s="150">
         <v>0.92</v>
       </c>
       <c r="F31" s="32">
@@ -5002,21 +4887,21 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="181">
+      <c r="B32" s="149">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="C32" s="181">
+      <c r="C32" s="149">
         <v>1103</v>
       </c>
-      <c r="D32" s="181" t="s">
+      <c r="D32" s="149" t="s">
         <v>92</v>
       </c>
-      <c r="E32" s="182">
+      <c r="E32" s="150">
         <v>1.43</v>
       </c>
       <c r="F32" s="32">
@@ -5062,21 +4947,21 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="181">
+      <c r="B33" s="149">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="C33" s="181">
+      <c r="C33" s="149">
         <v>1104</v>
       </c>
-      <c r="D33" s="181" t="s">
+      <c r="D33" s="149" t="s">
         <v>93</v>
       </c>
-      <c r="E33" s="182">
+      <c r="E33" s="150">
         <v>2.19</v>
       </c>
       <c r="F33" s="32">
@@ -5122,21 +5007,21 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="181">
+      <c r="B34" s="149">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="C34" s="181">
+      <c r="C34" s="149">
         <v>1105</v>
       </c>
-      <c r="D34" s="181" t="s">
+      <c r="D34" s="149" t="s">
         <v>94</v>
       </c>
-      <c r="E34" s="182">
+      <c r="E34" s="150">
         <v>1.94</v>
       </c>
       <c r="F34" s="32">
@@ -5183,21 +5068,21 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="181">
+      <c r="B35" s="149">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="C35" s="181">
+      <c r="C35" s="149">
         <v>2206</v>
       </c>
-      <c r="D35" s="181" t="s">
+      <c r="D35" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="E35" s="182">
+      <c r="E35" s="150">
         <v>2.17</v>
       </c>
       <c r="F35" s="32">
@@ -5247,21 +5132,21 @@
       </c>
       <c r="S35" s="21"/>
     </row>
-    <row r="36" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="181">
+      <c r="B36" s="149">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="C36" s="181">
+      <c r="C36" s="149">
         <v>2207</v>
       </c>
-      <c r="D36" s="181" t="s">
+      <c r="D36" s="149" t="s">
         <v>96</v>
       </c>
-      <c r="E36" s="182">
+      <c r="E36" s="150">
         <v>1.23</v>
       </c>
       <c r="F36" s="32">
@@ -5311,21 +5196,21 @@
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="181">
+      <c r="B37" s="149">
         <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="C37" s="181">
+      <c r="C37" s="149">
         <v>2208</v>
       </c>
-      <c r="D37" s="181" t="s">
+      <c r="D37" s="149" t="s">
         <v>97</v>
       </c>
-      <c r="E37" s="182">
+      <c r="E37" s="150">
         <v>1.29</v>
       </c>
       <c r="F37" s="32">
@@ -5372,21 +5257,21 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="181">
+      <c r="B38" s="149">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="C38" s="181">
+      <c r="C38" s="149">
         <v>2201</v>
       </c>
-      <c r="D38" s="181" t="s">
+      <c r="D38" s="149" t="s">
         <v>97</v>
       </c>
-      <c r="E38" s="182">
+      <c r="E38" s="150">
         <v>1.36</v>
       </c>
       <c r="F38" s="32">
@@ -5433,21 +5318,21 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B39" s="181">
+      <c r="B39" s="149">
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
-      <c r="C39" s="181">
+      <c r="C39" s="149">
         <v>2202</v>
       </c>
-      <c r="D39" s="181" t="s">
+      <c r="D39" s="149" t="s">
         <v>98</v>
       </c>
-      <c r="E39" s="182">
+      <c r="E39" s="150">
         <v>0.57999999999999996</v>
       </c>
       <c r="F39" s="32">
@@ -5497,21 +5382,21 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="B40" s="181">
+      <c r="B40" s="149">
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
-      <c r="C40" s="181">
+      <c r="C40" s="149">
         <v>2203</v>
       </c>
-      <c r="D40" s="181" t="s">
+      <c r="D40" s="149" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="182">
+      <c r="E40" s="150">
         <v>0.57999999999999996</v>
       </c>
       <c r="F40" s="32">
@@ -5546,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="87">
-        <f t="shared" ref="O40:O71" si="11">ROUND(SUM(I40:N40),0) + Q40</f>
+        <f t="shared" ref="O40:O66" si="11">ROUND(SUM(I40:N40),0) + Q40</f>
         <v>82080.320000000007</v>
       </c>
       <c r="P40" s="88">
@@ -5561,21 +5446,21 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="181">
+      <c r="B41" s="149">
         <f t="shared" si="6"/>
         <v>33</v>
       </c>
-      <c r="C41" s="181">
+      <c r="C41" s="149">
         <v>2204</v>
       </c>
-      <c r="D41" s="181" t="s">
+      <c r="D41" s="149" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="182">
+      <c r="E41" s="150">
         <v>1.36</v>
       </c>
       <c r="F41" s="32">
@@ -5625,21 +5510,21 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="181">
+      <c r="B42" s="149">
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-      <c r="C42" s="181">
+      <c r="C42" s="149">
         <v>2205</v>
       </c>
-      <c r="D42" s="181" t="s">
+      <c r="D42" s="149" t="s">
         <v>98</v>
       </c>
-      <c r="E42" s="182">
+      <c r="E42" s="150">
         <v>1.67</v>
       </c>
       <c r="F42" s="32">
@@ -5689,21 +5574,21 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="181">
+      <c r="B43" s="149">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="C43" s="181">
+      <c r="C43" s="149">
         <v>2206</v>
       </c>
-      <c r="D43" s="181" t="s">
+      <c r="D43" s="149" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="182">
+      <c r="E43" s="150">
         <v>2.17</v>
       </c>
       <c r="F43" s="32">
@@ -5753,21 +5638,21 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="181">
+      <c r="B44" s="149">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="C44" s="181">
+      <c r="C44" s="149">
         <v>2207</v>
       </c>
-      <c r="D44" s="181" t="s">
+      <c r="D44" s="149" t="s">
         <v>100</v>
       </c>
-      <c r="E44" s="182">
+      <c r="E44" s="150">
         <v>1.23</v>
       </c>
       <c r="F44" s="32">
@@ -5817,21 +5702,21 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="181">
+      <c r="B45" s="149">
         <f t="shared" si="6"/>
         <v>37</v>
       </c>
-      <c r="C45" s="181">
+      <c r="C45" s="149">
         <v>3308</v>
       </c>
-      <c r="D45" s="181" t="s">
+      <c r="D45" s="149" t="s">
         <v>123</v>
       </c>
-      <c r="E45" s="182">
+      <c r="E45" s="150">
         <v>1.23</v>
       </c>
       <c r="F45" s="32">
@@ -5878,21 +5763,21 @@
       </c>
       <c r="R45" s="72"/>
     </row>
-    <row r="46" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="B46" s="181">
+      <c r="B46" s="149">
         <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="C46" s="181">
+      <c r="C46" s="149">
         <v>3301</v>
       </c>
-      <c r="D46" s="184" t="s">
+      <c r="D46" s="152" t="s">
         <v>124</v>
       </c>
-      <c r="E46" s="182">
+      <c r="E46" s="150">
         <v>1.36</v>
       </c>
       <c r="F46" s="32">
@@ -5938,21 +5823,21 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="B47" s="181">
+      <c r="B47" s="149">
         <f>B46+1</f>
         <v>39</v>
       </c>
-      <c r="C47" s="181">
+      <c r="C47" s="149">
         <v>3302</v>
       </c>
-      <c r="D47" s="181" t="s">
+      <c r="D47" s="149" t="s">
         <v>101</v>
       </c>
-      <c r="E47" s="182">
+      <c r="E47" s="150">
         <v>0.57999999999999996</v>
       </c>
       <c r="F47" s="32">
@@ -5999,19 +5884,19 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="72"/>
-      <c r="B48" s="181">
+      <c r="B48" s="149">
         <f t="shared" ref="B48:B66" si="12">B47+1</f>
         <v>40</v>
       </c>
-      <c r="C48" s="181">
+      <c r="C48" s="149">
         <v>3303</v>
       </c>
-      <c r="D48" s="181" t="s">
+      <c r="D48" s="149" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="182">
+      <c r="E48" s="150">
         <v>0.57999999999999996</v>
       </c>
       <c r="F48" s="32">
@@ -6058,19 +5943,19 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="72"/>
-      <c r="B49" s="181">
+      <c r="B49" s="149">
         <f t="shared" si="12"/>
         <v>41</v>
       </c>
-      <c r="C49" s="181">
+      <c r="C49" s="149">
         <v>3304</v>
       </c>
-      <c r="D49" s="181" t="s">
+      <c r="D49" s="149" t="s">
         <v>130</v>
       </c>
-      <c r="E49" s="182">
+      <c r="E49" s="150">
         <v>1.36</v>
       </c>
       <c r="F49" s="32">
@@ -6116,19 +6001,19 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="72"/>
-      <c r="B50" s="181">
+      <c r="B50" s="149">
         <f t="shared" si="12"/>
         <v>42</v>
       </c>
-      <c r="C50" s="181">
+      <c r="C50" s="149">
         <v>3305</v>
       </c>
-      <c r="D50" s="181" t="s">
+      <c r="D50" s="149" t="s">
         <v>131</v>
       </c>
-      <c r="E50" s="182">
+      <c r="E50" s="150">
         <v>1.67</v>
       </c>
       <c r="F50" s="32">
@@ -6174,19 +6059,19 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="72"/>
-      <c r="B51" s="181">
+      <c r="B51" s="149">
         <f t="shared" si="12"/>
         <v>43</v>
       </c>
-      <c r="C51" s="181">
+      <c r="C51" s="149">
         <v>4406</v>
       </c>
-      <c r="D51" s="181" t="s">
+      <c r="D51" s="149" t="s">
         <v>132</v>
       </c>
-      <c r="E51" s="182">
+      <c r="E51" s="150">
         <v>2.17</v>
       </c>
       <c r="F51" s="32">
@@ -6233,19 +6118,19 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="72"/>
-      <c r="B52" s="181">
+      <c r="B52" s="149">
         <f t="shared" si="12"/>
         <v>44</v>
       </c>
-      <c r="C52" s="181">
+      <c r="C52" s="149">
         <v>4407</v>
       </c>
-      <c r="D52" s="181" t="s">
+      <c r="D52" s="149" t="s">
         <v>133</v>
       </c>
-      <c r="E52" s="182">
+      <c r="E52" s="150">
         <v>1.23</v>
       </c>
       <c r="F52" s="32">
@@ -6291,19 +6176,19 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="72"/>
-      <c r="B53" s="181">
+      <c r="B53" s="149">
         <f t="shared" si="12"/>
         <v>45</v>
       </c>
-      <c r="C53" s="181">
+      <c r="C53" s="149">
         <v>4408</v>
       </c>
-      <c r="D53" s="181" t="s">
+      <c r="D53" s="149" t="s">
         <v>134</v>
       </c>
-      <c r="E53" s="182">
+      <c r="E53" s="150">
         <v>1.29</v>
       </c>
       <c r="F53" s="32">
@@ -6349,19 +6234,19 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="72"/>
-      <c r="B54" s="181">
+      <c r="B54" s="149">
         <f t="shared" si="12"/>
         <v>46</v>
       </c>
-      <c r="C54" s="181">
+      <c r="C54" s="149">
         <v>4401</v>
       </c>
-      <c r="D54" s="181" t="s">
+      <c r="D54" s="149" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="182">
+      <c r="E54" s="150">
         <v>1.36</v>
       </c>
       <c r="F54" s="32">
@@ -6408,19 +6293,19 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="72"/>
-      <c r="B55" s="181">
+      <c r="B55" s="149">
         <f t="shared" si="12"/>
         <v>47</v>
       </c>
-      <c r="C55" s="181">
+      <c r="C55" s="149">
         <v>4402</v>
       </c>
-      <c r="D55" s="181" t="s">
+      <c r="D55" s="149" t="s">
         <v>136</v>
       </c>
-      <c r="E55" s="182">
+      <c r="E55" s="150">
         <v>0.57999999999999996</v>
       </c>
       <c r="F55" s="32">
@@ -6467,19 +6352,19 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="72"/>
-      <c r="B56" s="181">
+      <c r="B56" s="149">
         <f t="shared" si="12"/>
         <v>48</v>
       </c>
-      <c r="C56" s="181">
+      <c r="C56" s="149">
         <v>4403</v>
       </c>
-      <c r="D56" s="181" t="s">
+      <c r="D56" s="149" t="s">
         <v>137</v>
       </c>
-      <c r="E56" s="182">
+      <c r="E56" s="150">
         <v>0.57999999999999996</v>
       </c>
       <c r="F56" s="32">
@@ -6528,19 +6413,19 @@
         <v>152</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="72"/>
-      <c r="B57" s="181">
+      <c r="B57" s="149">
         <f t="shared" si="12"/>
         <v>49</v>
       </c>
-      <c r="C57" s="181">
+      <c r="C57" s="149">
         <v>4404</v>
       </c>
-      <c r="D57" s="181" t="s">
+      <c r="D57" s="149" t="s">
         <v>137</v>
       </c>
-      <c r="E57" s="182">
+      <c r="E57" s="150">
         <v>1.36</v>
       </c>
       <c r="F57" s="32">
@@ -6589,19 +6474,19 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="72"/>
-      <c r="B58" s="181">
+      <c r="B58" s="149">
         <f t="shared" si="12"/>
         <v>50</v>
       </c>
-      <c r="C58" s="181">
+      <c r="C58" s="149">
         <v>4405</v>
       </c>
-      <c r="D58" s="181" t="s">
+      <c r="D58" s="149" t="s">
         <v>137</v>
       </c>
-      <c r="E58" s="182">
+      <c r="E58" s="150">
         <v>1.67</v>
       </c>
       <c r="F58" s="32">
@@ -6650,19 +6535,19 @@
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="72"/>
-      <c r="B59" s="181">
+      <c r="B59" s="149">
         <f t="shared" si="12"/>
         <v>51</v>
       </c>
-      <c r="C59" s="181">
+      <c r="C59" s="149">
         <v>5506</v>
       </c>
-      <c r="D59" s="181" t="s">
+      <c r="D59" s="149" t="s">
         <v>138</v>
       </c>
-      <c r="E59" s="182">
+      <c r="E59" s="150">
         <v>2.17</v>
       </c>
       <c r="F59" s="32">
@@ -6708,19 +6593,19 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
-      <c r="B60" s="181">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A60" s="167"/>
+      <c r="B60" s="168">
         <f t="shared" si="12"/>
         <v>52</v>
       </c>
-      <c r="C60" s="181">
+      <c r="C60" s="168">
         <v>5507</v>
       </c>
-      <c r="D60" s="181" t="s">
+      <c r="D60" s="168" t="s">
         <v>139</v>
       </c>
-      <c r="E60" s="182">
+      <c r="E60" s="150">
         <v>1.79</v>
       </c>
       <c r="F60" s="32">
@@ -6766,19 +6651,19 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="72"/>
-      <c r="B61" s="181">
+      <c r="B61" s="149">
         <f t="shared" si="12"/>
         <v>53</v>
       </c>
-      <c r="C61" s="181">
+      <c r="C61" s="149">
         <v>5508</v>
       </c>
-      <c r="D61" s="181" t="s">
+      <c r="D61" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="E61" s="182">
+      <c r="E61" s="150">
         <v>1.29</v>
       </c>
       <c r="F61" s="32">
@@ -6824,22 +6709,22 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="72"/>
-      <c r="B62" s="181">
+      <c r="B62" s="164">
         <f t="shared" si="12"/>
         <v>54</v>
       </c>
-      <c r="C62" s="181">
+      <c r="C62" s="164">
         <v>5501</v>
       </c>
-      <c r="D62" s="181" t="s">
+      <c r="D62" s="164" t="s">
         <v>141</v>
       </c>
-      <c r="E62" s="182">
+      <c r="E62" s="165">
         <v>1.36</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="166">
         <v>221075.54</v>
       </c>
       <c r="G62" s="32">
@@ -6883,19 +6768,19 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="72"/>
-      <c r="B63" s="181">
+      <c r="B63" s="149">
         <f t="shared" si="12"/>
         <v>55</v>
       </c>
-      <c r="C63" s="181">
+      <c r="C63" s="149">
         <v>5503</v>
       </c>
-      <c r="D63" s="181" t="s">
+      <c r="D63" s="149" t="s">
         <v>142</v>
       </c>
-      <c r="E63" s="182">
+      <c r="E63" s="150">
         <v>0.57999999999999996</v>
       </c>
       <c r="F63" s="32">
@@ -6944,19 +6829,19 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="72"/>
-      <c r="B64" s="181">
+      <c r="B64" s="149">
         <f t="shared" si="12"/>
         <v>56</v>
       </c>
-      <c r="C64" s="181">
+      <c r="C64" s="149">
         <v>5504</v>
       </c>
-      <c r="D64" s="181" t="s">
+      <c r="D64" s="149" t="s">
         <v>82</v>
       </c>
-      <c r="E64" s="182">
+      <c r="E64" s="150">
         <v>1.36</v>
       </c>
       <c r="F64" s="32">
@@ -7005,19 +6890,19 @@
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="72"/>
-      <c r="B65" s="181">
+      <c r="B65" s="149">
         <f t="shared" si="12"/>
         <v>57</v>
       </c>
-      <c r="C65" s="181">
+      <c r="C65" s="149">
         <v>5502</v>
       </c>
-      <c r="D65" s="181" t="s">
+      <c r="D65" s="149" t="s">
         <v>78</v>
       </c>
-      <c r="E65" s="182">
+      <c r="E65" s="150">
         <v>0.57999999999999996</v>
       </c>
       <c r="F65" s="32">
@@ -7064,21 +6949,21 @@
         <v>0.57000000000000028</v>
       </c>
       <c r="R65" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B66" s="181">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B66" s="149">
         <f t="shared" si="12"/>
         <v>58</v>
       </c>
-      <c r="C66" s="181">
+      <c r="C66" s="149">
         <v>5505</v>
       </c>
-      <c r="D66" s="181" t="s">
+      <c r="D66" s="149" t="s">
         <v>143</v>
       </c>
-      <c r="E66" s="182">
+      <c r="E66" s="150">
         <v>1.67</v>
       </c>
       <c r="F66" s="32">
@@ -7125,7 +7010,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B67" s="83"/>
       <c r="C67" s="28"/>
       <c r="D67" s="28"/>
@@ -7143,7 +7028,7 @@
       <c r="P67" s="31"/>
       <c r="Q67" s="22"/>
     </row>
-    <row r="68" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="43"/>
       <c r="C68" s="44"/>
       <c r="D68" s="96"/>
@@ -7196,98 +7081,103 @@
         <v>34100637.109999999</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D69" s="24"/>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="214" t="s">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="192" t="s">
         <v>69</v>
       </c>
-      <c r="E71" s="214"/>
-      <c r="F71" s="214"/>
-      <c r="G71" s="214"/>
-      <c r="H71" s="214"/>
-      <c r="I71" s="214"/>
-      <c r="J71" s="214"/>
-      <c r="K71" s="214"/>
-      <c r="L71" s="214"/>
-      <c r="M71" s="214"/>
-      <c r="N71" s="214"/>
-      <c r="O71" s="214"/>
-    </row>
-    <row r="72" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="214"/>
-      <c r="E72" s="214"/>
-      <c r="F72" s="214"/>
-      <c r="G72" s="214"/>
-      <c r="H72" s="214"/>
-      <c r="I72" s="214"/>
-      <c r="J72" s="214"/>
-      <c r="K72" s="214"/>
-      <c r="L72" s="214"/>
-      <c r="M72" s="214"/>
-      <c r="N72" s="214"/>
-      <c r="O72" s="214"/>
-    </row>
-    <row r="73" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D73" s="214"/>
-      <c r="E73" s="214"/>
-      <c r="F73" s="214"/>
-      <c r="G73" s="214"/>
-      <c r="H73" s="214"/>
-      <c r="I73" s="214"/>
-      <c r="J73" s="214"/>
-      <c r="K73" s="214"/>
-      <c r="L73" s="214"/>
-      <c r="M73" s="214"/>
-      <c r="N73" s="214"/>
-      <c r="O73" s="214"/>
-    </row>
-    <row r="74" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D74" s="214"/>
-      <c r="E74" s="214"/>
-      <c r="F74" s="214"/>
-      <c r="G74" s="214"/>
-      <c r="H74" s="214"/>
-      <c r="I74" s="214"/>
-      <c r="J74" s="214"/>
-      <c r="K74" s="214"/>
-      <c r="L74" s="214"/>
-      <c r="M74" s="214"/>
-      <c r="N74" s="214"/>
-      <c r="O74" s="214"/>
-    </row>
-    <row r="75" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D75" s="214"/>
-      <c r="E75" s="214"/>
-      <c r="F75" s="214"/>
-      <c r="G75" s="214"/>
-      <c r="H75" s="214"/>
-      <c r="I75" s="214"/>
-      <c r="J75" s="214"/>
-      <c r="K75" s="214"/>
-      <c r="L75" s="214"/>
-      <c r="M75" s="214"/>
-      <c r="N75" s="214"/>
-      <c r="O75" s="214"/>
-    </row>
-    <row r="76" spans="1:18" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D76" s="214"/>
-      <c r="E76" s="214"/>
-      <c r="F76" s="214"/>
-      <c r="G76" s="214"/>
-      <c r="H76" s="214"/>
-      <c r="I76" s="214"/>
-      <c r="J76" s="214"/>
-      <c r="K76" s="214"/>
-      <c r="L76" s="214"/>
-      <c r="M76" s="214"/>
-      <c r="N76" s="214"/>
-      <c r="O76" s="214"/>
+      <c r="E71" s="192"/>
+      <c r="F71" s="192"/>
+      <c r="G71" s="192"/>
+      <c r="H71" s="192"/>
+      <c r="I71" s="192"/>
+      <c r="J71" s="192"/>
+      <c r="K71" s="192"/>
+      <c r="L71" s="192"/>
+      <c r="M71" s="192"/>
+      <c r="N71" s="192"/>
+      <c r="O71" s="192"/>
+    </row>
+    <row r="72" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D72" s="192"/>
+      <c r="E72" s="192"/>
+      <c r="F72" s="192"/>
+      <c r="G72" s="192"/>
+      <c r="H72" s="192"/>
+      <c r="I72" s="192"/>
+      <c r="J72" s="192"/>
+      <c r="K72" s="192"/>
+      <c r="L72" s="192"/>
+      <c r="M72" s="192"/>
+      <c r="N72" s="192"/>
+      <c r="O72" s="192"/>
+    </row>
+    <row r="73" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="192"/>
+      <c r="E73" s="192"/>
+      <c r="F73" s="192"/>
+      <c r="G73" s="192"/>
+      <c r="H73" s="192"/>
+      <c r="I73" s="192"/>
+      <c r="J73" s="192"/>
+      <c r="K73" s="192"/>
+      <c r="L73" s="192"/>
+      <c r="M73" s="192"/>
+      <c r="N73" s="192"/>
+      <c r="O73" s="192"/>
+    </row>
+    <row r="74" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D74" s="192"/>
+      <c r="E74" s="192"/>
+      <c r="F74" s="192"/>
+      <c r="G74" s="192"/>
+      <c r="H74" s="192"/>
+      <c r="I74" s="192"/>
+      <c r="J74" s="192"/>
+      <c r="K74" s="192"/>
+      <c r="L74" s="192"/>
+      <c r="M74" s="192"/>
+      <c r="N74" s="192"/>
+      <c r="O74" s="192"/>
+    </row>
+    <row r="75" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D75" s="192"/>
+      <c r="E75" s="192"/>
+      <c r="F75" s="192"/>
+      <c r="G75" s="192"/>
+      <c r="H75" s="192"/>
+      <c r="I75" s="192"/>
+      <c r="J75" s="192"/>
+      <c r="K75" s="192"/>
+      <c r="L75" s="192"/>
+      <c r="M75" s="192"/>
+      <c r="N75" s="192"/>
+      <c r="O75" s="192"/>
+    </row>
+    <row r="76" spans="1:18" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D76" s="192"/>
+      <c r="E76" s="192"/>
+      <c r="F76" s="192"/>
+      <c r="G76" s="192"/>
+      <c r="H76" s="192"/>
+      <c r="I76" s="192"/>
+      <c r="J76" s="192"/>
+      <c r="K76" s="192"/>
+      <c r="L76" s="192"/>
+      <c r="M76" s="192"/>
+      <c r="N76" s="192"/>
+      <c r="O76" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="D71:O76"/>
@@ -7302,11 +7192,6 @@
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="B5:P5"/>
     <mergeCell ref="M6:M7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -7315,14 +7200,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
-  <dimension ref="C2:K73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C2:K24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-    </row>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+    </row>
+    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C3" s="111" t="s">
         <v>153</v>
       </c>
@@ -7333,618 +7219,186 @@
       <c r="F3" s="108"/>
       <c r="G3" s="108"/>
       <c r="H3" s="109"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-    </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="72"/>
+    </row>
+    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C4" s="113" t="s">
         <v>154</v>
       </c>
       <c r="D4" s="114">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H4" s="110"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-    </row>
-    <row r="5" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="72"/>
+    </row>
+    <row r="5" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="113"/>
       <c r="D5" s="114"/>
       <c r="H5" s="110"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="185"/>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C6" s="229" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="230"/>
-      <c r="E6" s="230"/>
-      <c r="F6" s="230"/>
-      <c r="G6" s="230"/>
-      <c r="H6" s="231"/>
-      <c r="I6" s="185"/>
-      <c r="J6" s="185"/>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C7" s="232"/>
-      <c r="D7" s="233"/>
-      <c r="E7" s="233"/>
-      <c r="F7" s="233"/>
-      <c r="G7" s="233"/>
-      <c r="H7" s="234"/>
-      <c r="I7" s="185"/>
-      <c r="J7" s="185"/>
-    </row>
-    <row r="8" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="235"/>
-      <c r="D8" s="236"/>
-      <c r="E8" s="236"/>
-      <c r="F8" s="236"/>
-      <c r="G8" s="236"/>
-      <c r="H8" s="237"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="118"/>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-    </row>
-    <row r="10" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C11" s="145" t="s">
+      <c r="I5" s="222"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="72"/>
+    </row>
+    <row r="6" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C6" s="213" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="214"/>
+      <c r="E6" s="214"/>
+      <c r="F6" s="214"/>
+      <c r="G6" s="214"/>
+      <c r="H6" s="215"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="72"/>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="216"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="218"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="72"/>
+    </row>
+    <row r="8" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="219"/>
+      <c r="D8" s="220"/>
+      <c r="E8" s="220"/>
+      <c r="F8" s="220"/>
+      <c r="G8" s="220"/>
+      <c r="H8" s="221"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+    </row>
+    <row r="10" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C11" s="169" t="s">
         <v>153</v>
       </c>
-      <c r="D11" s="146">
-        <v>1</v>
+      <c r="D11" s="170">
+        <f>D3+1</f>
+        <v>2</v>
       </c>
       <c r="E11" s="108"/>
       <c r="F11" s="108"/>
       <c r="G11" s="108"/>
       <c r="H11" s="109"/>
-      <c r="I11" s="118"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="118"/>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C12" s="147" t="s">
+    </row>
+    <row r="12" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C12" s="171" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="148">
-        <v>57</v>
+      <c r="D12" s="167" t="s">
+        <v>203</v>
       </c>
       <c r="H12" s="110"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
-      <c r="K12" s="118"/>
-    </row>
-    <row r="13" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="147"/>
-      <c r="D13" s="148"/>
+    </row>
+    <row r="13" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="171"/>
+      <c r="D13" s="167"/>
       <c r="H13" s="110"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="118"/>
-    </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C14" s="229" t="s">
-        <v>165</v>
-      </c>
-      <c r="D14" s="230"/>
-      <c r="E14" s="230"/>
-      <c r="F14" s="230"/>
-      <c r="G14" s="230"/>
-      <c r="H14" s="231"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
-    </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C15" s="232"/>
-      <c r="D15" s="233"/>
-      <c r="E15" s="233"/>
-      <c r="F15" s="233"/>
-      <c r="G15" s="233"/>
-      <c r="H15" s="234"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="118"/>
-      <c r="K15" s="118"/>
-    </row>
-    <row r="16" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="235"/>
-      <c r="D16" s="236"/>
-      <c r="E16" s="236"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="236"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-    </row>
-    <row r="18" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C19" s="149" t="s">
+    </row>
+    <row r="14" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C14" s="213" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" s="214"/>
+      <c r="E14" s="214"/>
+      <c r="F14" s="214"/>
+      <c r="G14" s="214"/>
+      <c r="H14" s="215"/>
+    </row>
+    <row r="15" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C15" s="216"/>
+      <c r="D15" s="217"/>
+      <c r="E15" s="217"/>
+      <c r="F15" s="217"/>
+      <c r="G15" s="217"/>
+      <c r="H15" s="218"/>
+    </row>
+    <row r="16" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C16" s="219"/>
+      <c r="D16" s="220"/>
+      <c r="E16" s="220"/>
+      <c r="F16" s="220"/>
+      <c r="G16" s="220"/>
+      <c r="H16" s="221"/>
+    </row>
+    <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C19" s="223" t="s">
         <v>153</v>
       </c>
-      <c r="D19" s="150">
-        <v>1</v>
+      <c r="D19" s="224">
+        <f>D11+1</f>
+        <v>3</v>
       </c>
       <c r="E19" s="108"/>
       <c r="F19" s="108"/>
       <c r="G19" s="108"/>
       <c r="H19" s="109"/>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C20" s="151" t="s">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="225" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="152">
-        <v>55</v>
+      <c r="D20" s="226" t="s">
+        <v>203</v>
       </c>
       <c r="F20" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="H20" s="110"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118"/>
-    </row>
-    <row r="21" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="151"/>
-      <c r="D21" s="152"/>
+    </row>
+    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="225"/>
+      <c r="D21" s="226"/>
       <c r="H21" s="110"/>
-      <c r="I21" s="118"/>
-      <c r="J21" s="118"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C22" s="229" t="s">
-        <v>164</v>
-      </c>
-      <c r="D22" s="230"/>
-      <c r="E22" s="230"/>
-      <c r="F22" s="230"/>
-      <c r="G22" s="230"/>
-      <c r="H22" s="231"/>
-      <c r="I22" s="118"/>
-      <c r="J22" s="118"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C23" s="232"/>
-      <c r="D23" s="233"/>
-      <c r="E23" s="233"/>
-      <c r="F23" s="233"/>
-      <c r="G23" s="233"/>
-      <c r="H23" s="234"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-    </row>
-    <row r="24" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="235"/>
-      <c r="D24" s="236"/>
-      <c r="E24" s="236"/>
-      <c r="F24" s="236"/>
-      <c r="G24" s="236"/>
-      <c r="H24" s="237"/>
-    </row>
-    <row r="26" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C27" s="153" t="s">
-        <v>153</v>
-      </c>
-      <c r="D27" s="154">
-        <v>1</v>
-      </c>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="118"/>
-      <c r="J27" s="118"/>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C28" s="155" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" s="156">
-        <v>52</v>
-      </c>
-      <c r="H28" s="110"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="118"/>
-    </row>
-    <row r="29" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="155"/>
-      <c r="D29" s="156"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="118"/>
-      <c r="J29" s="118"/>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C30" s="229" t="s">
-        <v>166</v>
-      </c>
-      <c r="D30" s="230"/>
-      <c r="E30" s="230"/>
-      <c r="F30" s="230"/>
-      <c r="G30" s="230"/>
-      <c r="H30" s="231"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C31" s="232"/>
-      <c r="D31" s="233"/>
-      <c r="E31" s="233"/>
-      <c r="F31" s="233"/>
-      <c r="G31" s="233"/>
-      <c r="H31" s="234"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="118"/>
-    </row>
-    <row r="32" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="235"/>
-      <c r="D32" s="236"/>
-      <c r="E32" s="236"/>
-      <c r="F32" s="236"/>
-      <c r="G32" s="236"/>
-      <c r="H32" s="237"/>
-    </row>
-    <row r="34" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="157" t="s">
-        <v>153</v>
-      </c>
-      <c r="D35" s="158">
-        <v>1</v>
-      </c>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="108"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="118"/>
-      <c r="J35" s="118"/>
-    </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="159" t="s">
-        <v>154</v>
-      </c>
-      <c r="D36" s="160" t="s">
-        <v>168</v>
-      </c>
-      <c r="F36" t="s">
-        <v>169</v>
-      </c>
-      <c r="H36" s="110"/>
-      <c r="I36" s="118"/>
-      <c r="J36" s="118"/>
-    </row>
-    <row r="37" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="159"/>
-      <c r="D37" s="160"/>
-      <c r="H37" s="110"/>
-      <c r="I37" s="118"/>
-      <c r="J37" s="118"/>
-    </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C38" s="229" t="s">
-        <v>174</v>
-      </c>
-      <c r="D38" s="230"/>
-      <c r="E38" s="230"/>
-      <c r="F38" s="230"/>
-      <c r="G38" s="230"/>
-      <c r="H38" s="231"/>
-      <c r="I38" s="118"/>
-      <c r="J38" s="118"/>
-    </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C39" s="232"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="234"/>
-      <c r="I39" s="118"/>
-      <c r="J39" s="118"/>
-    </row>
-    <row r="40" spans="3:10" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="235"/>
-      <c r="D40" s="236"/>
-      <c r="E40" s="236"/>
-      <c r="F40" s="236"/>
-      <c r="G40" s="236"/>
-      <c r="H40" s="237"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="118"/>
-    </row>
-    <row r="42" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C43" s="161" t="s">
-        <v>153</v>
-      </c>
-      <c r="D43" s="162">
-        <v>1</v>
-      </c>
-      <c r="E43" s="108"/>
-      <c r="F43" s="108"/>
-      <c r="G43" s="108"/>
-      <c r="H43" s="109"/>
-      <c r="I43" s="118"/>
-      <c r="J43" s="118"/>
-    </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C44" s="163" t="s">
-        <v>154</v>
-      </c>
-      <c r="D44" s="164" t="s">
-        <v>170</v>
-      </c>
-      <c r="H44" s="110"/>
-      <c r="I44" s="118"/>
-      <c r="J44" s="118"/>
-    </row>
-    <row r="45" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="163"/>
-      <c r="D45" s="164"/>
-      <c r="H45" s="110"/>
-      <c r="I45" s="118"/>
-      <c r="J45" s="118"/>
-    </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C46" s="229" t="s">
-        <v>183</v>
-      </c>
-      <c r="D46" s="230"/>
-      <c r="E46" s="230"/>
-      <c r="F46" s="230"/>
-      <c r="G46" s="230"/>
-      <c r="H46" s="231"/>
-      <c r="I46" s="118"/>
-      <c r="J46" s="118"/>
-    </row>
-    <row r="47" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C47" s="232"/>
-      <c r="D47" s="233"/>
-      <c r="E47" s="233"/>
-      <c r="F47" s="233"/>
-      <c r="G47" s="233"/>
-      <c r="H47" s="234"/>
-      <c r="I47" s="118"/>
-      <c r="J47" s="118"/>
-    </row>
-    <row r="48" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="235"/>
-      <c r="D48" s="236"/>
-      <c r="E48" s="236"/>
-      <c r="F48" s="236"/>
-      <c r="G48" s="236"/>
-      <c r="H48" s="237"/>
-      <c r="I48" s="118"/>
-      <c r="J48" s="118"/>
-    </row>
-    <row r="50" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C51" s="165" t="s">
-        <v>153</v>
-      </c>
-      <c r="D51" s="166">
-        <v>1</v>
-      </c>
-      <c r="E51" s="108"/>
-      <c r="F51" s="108"/>
-      <c r="G51" s="108"/>
-      <c r="H51" s="109"/>
-    </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C52" s="167" t="s">
-        <v>154</v>
-      </c>
-      <c r="D52" s="168" t="s">
-        <v>172</v>
-      </c>
-      <c r="F52" t="s">
-        <v>171</v>
-      </c>
-      <c r="H52" s="110"/>
-      <c r="I52" s="118"/>
-      <c r="J52" s="118"/>
-    </row>
-    <row r="53" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="167"/>
-      <c r="D53" s="168"/>
-      <c r="H53" s="110"/>
-      <c r="I53" s="118"/>
-      <c r="J53" s="118"/>
-    </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C54" s="229" t="s">
-        <v>173</v>
-      </c>
-      <c r="D54" s="230"/>
-      <c r="E54" s="230"/>
-      <c r="F54" s="230"/>
-      <c r="G54" s="230"/>
-      <c r="H54" s="231"/>
-      <c r="I54" s="118"/>
-      <c r="J54" s="118"/>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C55" s="232"/>
-      <c r="D55" s="233"/>
-      <c r="E55" s="233"/>
-      <c r="F55" s="233"/>
-      <c r="G55" s="233"/>
-      <c r="H55" s="234"/>
-      <c r="I55" s="118"/>
-      <c r="J55" s="118"/>
-    </row>
-    <row r="56" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="235"/>
-      <c r="D56" s="236"/>
-      <c r="E56" s="236"/>
-      <c r="F56" s="236"/>
-      <c r="G56" s="236"/>
-      <c r="H56" s="237"/>
-      <c r="I56" s="118"/>
-      <c r="J56" s="118"/>
-    </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I57" s="118"/>
-      <c r="J57" s="118"/>
-    </row>
-    <row r="58" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C59" s="169" t="s">
-        <v>153</v>
-      </c>
-      <c r="D59" s="170">
-        <v>1</v>
-      </c>
-      <c r="E59" s="108"/>
-      <c r="F59" s="108"/>
-      <c r="G59" s="108"/>
-      <c r="H59" s="109"/>
-      <c r="I59" s="118"/>
-      <c r="J59" s="118"/>
-    </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C60" s="171" t="s">
-        <v>154</v>
-      </c>
-      <c r="D60" s="172" t="s">
-        <v>175</v>
-      </c>
-      <c r="H60" s="110"/>
-      <c r="I60" s="118"/>
-      <c r="J60" s="118"/>
-    </row>
-    <row r="61" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="171"/>
-      <c r="D61" s="172"/>
-      <c r="H61" s="110"/>
-      <c r="I61" s="118"/>
-      <c r="J61" s="118"/>
-    </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C62" s="229" t="s">
-        <v>176</v>
-      </c>
-      <c r="D62" s="230"/>
-      <c r="E62" s="230"/>
-      <c r="F62" s="230"/>
-      <c r="G62" s="230"/>
-      <c r="H62" s="231"/>
-      <c r="I62" s="118"/>
-      <c r="J62" s="118"/>
-    </row>
-    <row r="63" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C63" s="232"/>
-      <c r="D63" s="233"/>
-      <c r="E63" s="233"/>
-      <c r="F63" s="233"/>
-      <c r="G63" s="233"/>
-      <c r="H63" s="234"/>
-      <c r="I63" s="118"/>
-      <c r="J63" s="118"/>
-    </row>
-    <row r="64" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="235"/>
-      <c r="D64" s="236"/>
-      <c r="E64" s="236"/>
-      <c r="F64" s="236"/>
-      <c r="G64" s="236"/>
-      <c r="H64" s="237"/>
-    </row>
-    <row r="66" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="67" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C67" s="173" t="s">
-        <v>153</v>
-      </c>
-      <c r="D67" s="174">
-        <v>1</v>
-      </c>
-      <c r="E67" s="108"/>
-      <c r="F67" s="108"/>
-      <c r="G67" s="108"/>
-      <c r="H67" s="109"/>
-      <c r="I67" s="118"/>
-      <c r="J67" s="118"/>
-      <c r="K67" s="118"/>
-    </row>
-    <row r="68" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C68" s="175" t="s">
-        <v>154</v>
-      </c>
-      <c r="D68" s="176" t="s">
-        <v>178</v>
-      </c>
-      <c r="G68" t="s">
-        <v>178</v>
-      </c>
-      <c r="H68" s="110"/>
-      <c r="I68" s="118"/>
-      <c r="J68" s="118"/>
-      <c r="K68" s="118"/>
-    </row>
-    <row r="69" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="175"/>
-      <c r="D69" s="176"/>
-      <c r="H69" s="110"/>
-      <c r="I69" s="118"/>
-      <c r="J69" s="118"/>
-      <c r="K69" s="118"/>
-    </row>
-    <row r="70" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C70" s="229" t="s">
-        <v>177</v>
-      </c>
-      <c r="D70" s="230"/>
-      <c r="E70" s="230"/>
-      <c r="F70" s="230"/>
-      <c r="G70" s="230"/>
-      <c r="H70" s="231"/>
-      <c r="I70" s="118"/>
-      <c r="J70" s="118"/>
-      <c r="K70" s="118"/>
-    </row>
-    <row r="71" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C71" s="232"/>
-      <c r="D71" s="233"/>
-      <c r="E71" s="233"/>
-      <c r="F71" s="233"/>
-      <c r="G71" s="233"/>
-      <c r="H71" s="234"/>
-      <c r="I71" s="118"/>
-      <c r="J71" s="118"/>
-      <c r="K71" s="118"/>
-    </row>
-    <row r="72" spans="3:11" ht="67.150000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="235"/>
-      <c r="D72" s="236"/>
-      <c r="E72" s="236"/>
-      <c r="F72" s="236"/>
-      <c r="G72" s="236"/>
-      <c r="H72" s="237"/>
-      <c r="I72" s="118"/>
-      <c r="J72" s="118"/>
-      <c r="K72" s="118"/>
-    </row>
-    <row r="73" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="I73" s="118"/>
-      <c r="J73" s="118"/>
-      <c r="K73" s="118"/>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C22" s="213" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22" s="214"/>
+      <c r="E22" s="214"/>
+      <c r="F22" s="214"/>
+      <c r="G22" s="214"/>
+      <c r="H22" s="215"/>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C23" s="216"/>
+      <c r="D23" s="217"/>
+      <c r="E23" s="217"/>
+      <c r="F23" s="217"/>
+      <c r="G23" s="217"/>
+      <c r="H23" s="218"/>
+    </row>
+    <row r="24" spans="3:8" ht="62.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C24" s="219"/>
+      <c r="D24" s="220"/>
+      <c r="E24" s="220"/>
+      <c r="F24" s="220"/>
+      <c r="G24" s="220"/>
+      <c r="H24" s="221"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="C62:H64"/>
-    <mergeCell ref="C70:H72"/>
-    <mergeCell ref="C54:H56"/>
-    <mergeCell ref="C46:H48"/>
+  <mergeCells count="3">
     <mergeCell ref="C6:H8"/>
     <mergeCell ref="C14:H16"/>
     <mergeCell ref="C22:H24"/>
-    <mergeCell ref="C30:H32"/>
-    <mergeCell ref="C38:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7953,38 +7407,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA6BF67-58D9-44B8-9885-F86EBBDE6C60}">
   <dimension ref="A7:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="177">
+        <v>163</v>
+      </c>
+      <c r="D7" s="145">
         <v>712896.01</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" s="177">
+        <v>164</v>
+      </c>
+      <c r="D8" s="145">
         <v>476368</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D9">
         <v>13644</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D11" s="22">
         <f>D7-D8-D9</f>
